--- a/students_import2.xlsx
+++ b/students_import2.xlsx
@@ -1,25 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEFAULT\FPT\SEP-G58\Code\EDUCEN-SEP490-\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\FPT\Sem9-SP26\SEP\EDUCEN-SEP490-\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC619A51-2F18-4DAE-A1ED-D873049F4338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12915"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="students_import" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="178">
   <si>
     <t>Username</t>
   </si>
@@ -106,13 +110,460 @@
   </si>
   <si>
     <t>PhoneNumber</t>
+  </si>
+  <si>
+    <t>test006</t>
+  </si>
+  <si>
+    <t>Nguyen Van F</t>
+  </si>
+  <si>
+    <t>test006@email.com</t>
+  </si>
+  <si>
+    <t>test007</t>
+  </si>
+  <si>
+    <t>Nguyen Van G</t>
+  </si>
+  <si>
+    <t>test007@email.com</t>
+  </si>
+  <si>
+    <t>test008</t>
+  </si>
+  <si>
+    <t>Nguyen Van H</t>
+  </si>
+  <si>
+    <t>test008@email.com</t>
+  </si>
+  <si>
+    <t>10C</t>
+  </si>
+  <si>
+    <t>test009</t>
+  </si>
+  <si>
+    <t>Nguyen Van I</t>
+  </si>
+  <si>
+    <t>test009@email.com</t>
+  </si>
+  <si>
+    <t>test010</t>
+  </si>
+  <si>
+    <t>Nguyen Van J</t>
+  </si>
+  <si>
+    <t>test010@email.com</t>
+  </si>
+  <si>
+    <t>test011</t>
+  </si>
+  <si>
+    <t>Nguyen Van K</t>
+  </si>
+  <si>
+    <t>test011@email.com</t>
+  </si>
+  <si>
+    <t>test012</t>
+  </si>
+  <si>
+    <t>Nguyen Van L</t>
+  </si>
+  <si>
+    <t>test012@email.com</t>
+  </si>
+  <si>
+    <t>test013</t>
+  </si>
+  <si>
+    <t>Nguyen Van M</t>
+  </si>
+  <si>
+    <t>test013@email.com</t>
+  </si>
+  <si>
+    <t>test014</t>
+  </si>
+  <si>
+    <t>Nguyen Van N</t>
+  </si>
+  <si>
+    <t>test014@email.com</t>
+  </si>
+  <si>
+    <t>test015</t>
+  </si>
+  <si>
+    <t>Nguyen Van O</t>
+  </si>
+  <si>
+    <t>test015@email.com</t>
+  </si>
+  <si>
+    <t>test016</t>
+  </si>
+  <si>
+    <t>Nguyen Van P</t>
+  </si>
+  <si>
+    <t>test016@email.com</t>
+  </si>
+  <si>
+    <t>test017</t>
+  </si>
+  <si>
+    <t>Nguyen Van Q</t>
+  </si>
+  <si>
+    <t>test017@email.com</t>
+  </si>
+  <si>
+    <t>test018</t>
+  </si>
+  <si>
+    <t>Nguyen Van R</t>
+  </si>
+  <si>
+    <t>test018@email.com</t>
+  </si>
+  <si>
+    <t>11C</t>
+  </si>
+  <si>
+    <t>test019</t>
+  </si>
+  <si>
+    <t>Nguyen Van S</t>
+  </si>
+  <si>
+    <t>test019@email.com</t>
+  </si>
+  <si>
+    <t>test020</t>
+  </si>
+  <si>
+    <t>Nguyen Van T</t>
+  </si>
+  <si>
+    <t>test020@email.com</t>
+  </si>
+  <si>
+    <t>test021</t>
+  </si>
+  <si>
+    <t>Nguyen Van U</t>
+  </si>
+  <si>
+    <t>test021@email.com</t>
+  </si>
+  <si>
+    <t>test022</t>
+  </si>
+  <si>
+    <t>Nguyen Van V</t>
+  </si>
+  <si>
+    <t>test022@email.com</t>
+  </si>
+  <si>
+    <t>test023</t>
+  </si>
+  <si>
+    <t>Nguyen Van W</t>
+  </si>
+  <si>
+    <t>test023@email.com</t>
+  </si>
+  <si>
+    <t>test024</t>
+  </si>
+  <si>
+    <t>Nguyen Van X</t>
+  </si>
+  <si>
+    <t>test024@email.com</t>
+  </si>
+  <si>
+    <t>test025</t>
+  </si>
+  <si>
+    <t>Nguyen Van Y</t>
+  </si>
+  <si>
+    <t>test025@email.com</t>
+  </si>
+  <si>
+    <t>test026</t>
+  </si>
+  <si>
+    <t>Nguyen Van Z</t>
+  </si>
+  <si>
+    <t>test026@email.com</t>
+  </si>
+  <si>
+    <t>test027</t>
+  </si>
+  <si>
+    <t>Nguyen Van AA</t>
+  </si>
+  <si>
+    <t>test027@email.com</t>
+  </si>
+  <si>
+    <t>12B</t>
+  </si>
+  <si>
+    <t>test028</t>
+  </si>
+  <si>
+    <t>Nguyen Van AB</t>
+  </si>
+  <si>
+    <t>test028@email.com</t>
+  </si>
+  <si>
+    <t>12C</t>
+  </si>
+  <si>
+    <t>test029</t>
+  </si>
+  <si>
+    <t>Nguyen Van AC</t>
+  </si>
+  <si>
+    <t>test029@email.com</t>
+  </si>
+  <si>
+    <t>test030</t>
+  </si>
+  <si>
+    <t>Nguyen Van AD</t>
+  </si>
+  <si>
+    <t>test030@email.com</t>
+  </si>
+  <si>
+    <t>test031</t>
+  </si>
+  <si>
+    <t>Nguyen Van AE</t>
+  </si>
+  <si>
+    <t>test031@email.com</t>
+  </si>
+  <si>
+    <t>test032</t>
+  </si>
+  <si>
+    <t>Nguyen Van AF</t>
+  </si>
+  <si>
+    <t>test032@email.com</t>
+  </si>
+  <si>
+    <t>test033</t>
+  </si>
+  <si>
+    <t>Nguyen Van AG</t>
+  </si>
+  <si>
+    <t>test033@email.com</t>
+  </si>
+  <si>
+    <t>test034</t>
+  </si>
+  <si>
+    <t>Nguyen Van AH</t>
+  </si>
+  <si>
+    <t>test034@email.com</t>
+  </si>
+  <si>
+    <t>test035</t>
+  </si>
+  <si>
+    <t>Nguyen Van AI</t>
+  </si>
+  <si>
+    <t>test035@email.com</t>
+  </si>
+  <si>
+    <t>test036</t>
+  </si>
+  <si>
+    <t>Nguyen Van 36</t>
+  </si>
+  <si>
+    <t>test036@gmail.com</t>
+  </si>
+  <si>
+    <t>14A</t>
+  </si>
+  <si>
+    <t>aaa</t>
+  </si>
+  <si>
+    <t>aaaaaaa</t>
+  </si>
+  <si>
+    <t>test037</t>
+  </si>
+  <si>
+    <t>Nguyen van 37</t>
+  </si>
+  <si>
+    <t>test037@gmail.com</t>
+  </si>
+  <si>
+    <t>test038</t>
+  </si>
+  <si>
+    <t>Nguyen Van 38</t>
+  </si>
+  <si>
+    <t>test038@gmail.com</t>
+  </si>
+  <si>
+    <t>test45</t>
+  </si>
+  <si>
+    <t>Nguyen Van 45</t>
+  </si>
+  <si>
+    <t>test045@gmail.com</t>
+  </si>
+  <si>
+    <t>test46</t>
+  </si>
+  <si>
+    <t>aaaaaaaa</t>
+  </si>
+  <si>
+    <t>aaaaaa</t>
+  </si>
+  <si>
+    <t>Nuguyen van 46</t>
+  </si>
+  <si>
+    <t>test046@gmail.com</t>
+  </si>
+  <si>
+    <t>test47</t>
+  </si>
+  <si>
+    <t>nguyen van 47</t>
+  </si>
+  <si>
+    <t>12D</t>
+  </si>
+  <si>
+    <t>test047@gmail.com</t>
+  </si>
+  <si>
+    <t>aaaaa</t>
+  </si>
+  <si>
+    <t>test048</t>
+  </si>
+  <si>
+    <t>Nguyen van 48</t>
+  </si>
+  <si>
+    <t>test048@gmail.com</t>
+  </si>
+  <si>
+    <t>test049</t>
+  </si>
+  <si>
+    <t>nguyen van 49</t>
+  </si>
+  <si>
+    <t>test049@gmail.com</t>
+  </si>
+  <si>
+    <t>test050</t>
+  </si>
+  <si>
+    <t>nguyen van 50</t>
+  </si>
+  <si>
+    <t>test050@gmail.com</t>
+  </si>
+  <si>
+    <t>test051</t>
+  </si>
+  <si>
+    <t>nguyen van 51</t>
+  </si>
+  <si>
+    <t>test051@gmail.com</t>
+  </si>
+  <si>
+    <t>test052</t>
+  </si>
+  <si>
+    <t>nguyen van 52</t>
+  </si>
+  <si>
+    <t>test052@gmail.com</t>
+  </si>
+  <si>
+    <t>test053</t>
+  </si>
+  <si>
+    <t>test054</t>
+  </si>
+  <si>
+    <t>nguyen van 53</t>
+  </si>
+  <si>
+    <t>test053@gmail.com</t>
+  </si>
+  <si>
+    <t>nguyen van 54</t>
+  </si>
+  <si>
+    <t>test054@gmail.com</t>
+  </si>
+  <si>
+    <t>test055</t>
+  </si>
+  <si>
+    <t>nguyen van 55</t>
+  </si>
+  <si>
+    <t>test055@gmail.com</t>
+  </si>
+  <si>
+    <t>test056</t>
+  </si>
+  <si>
+    <t>test057</t>
+  </si>
+  <si>
+    <t>nguyen van 56</t>
+  </si>
+  <si>
+    <t>test056@gmail.com</t>
+  </si>
+  <si>
+    <t>nguyen van 57</t>
+  </si>
+  <si>
+    <t>test057@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,6 +698,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -545,7 +1017,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -588,12 +1060,15 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -627,6 +1102,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -912,19 +1388,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" customWidth="1"/>
-    <col min="2" max="2" width="31.140625" customWidth="1"/>
-    <col min="3" max="3" width="33.85546875" customWidth="1"/>
-    <col min="4" max="4" width="37.42578125" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" customWidth="1"/>
-    <col min="6" max="6" width="32.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.88671875" customWidth="1"/>
+    <col min="2" max="2" width="31.109375" customWidth="1"/>
+    <col min="3" max="3" width="33.88671875" customWidth="1"/>
+    <col min="4" max="4" width="37.44140625" customWidth="1"/>
+    <col min="5" max="5" width="17.88671875" customWidth="1"/>
+    <col min="6" max="6" width="32.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -947,7 +1423,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -970,7 +1446,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -993,7 +1469,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1016,7 +1492,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1039,7 +1515,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1065,4 +1541,1217 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88768A2A-C4B2-4A5B-B985-03C8CBA6A2F0}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="33.33203125" customWidth="1"/>
+    <col min="3" max="3" width="35.33203125" customWidth="1"/>
+    <col min="4" max="4" width="25.44140625" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" customWidth="1"/>
+    <col min="6" max="6" width="36.21875" customWidth="1"/>
+    <col min="7" max="7" width="22.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2">
+        <v>901234572</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1">
+        <v>38515</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3">
+        <v>901234573</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1">
+        <v>38547</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4">
+        <v>901234574</v>
+      </c>
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="1">
+        <v>38580</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5">
+        <v>901234575</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1">
+        <v>38613</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6">
+        <v>901234576</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="1">
+        <v>38645</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7">
+        <v>901234577</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="1">
+        <v>38678</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8">
+        <v>901234578</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="1">
+        <v>38710</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9">
+        <v>901234579</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="1">
+        <v>38722</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10">
+        <v>901234580</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="1">
+        <v>38755</v>
+      </c>
+      <c r="G10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11">
+        <v>901234581</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="1">
+        <v>38785</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06953985-C075-4BB3-A447-6CAD8C73ED67}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2">
+        <v>901234582</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="1">
+        <v>38818</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3">
+        <v>901234583</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="1">
+        <v>38850</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4">
+        <v>901234584</v>
+      </c>
+      <c r="E4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="1">
+        <v>38883</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5">
+        <v>901234585</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="1">
+        <v>38915</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6">
+        <v>901234586</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="1">
+        <v>38948</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7">
+        <v>901234587</v>
+      </c>
+      <c r="E7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="1">
+        <v>38981</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8">
+        <v>901234588</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="1">
+        <v>39013</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9">
+        <v>901234589</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="1">
+        <v>39046</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10">
+        <v>901234590</v>
+      </c>
+      <c r="E10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="1">
+        <v>39078</v>
+      </c>
+      <c r="G10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11">
+        <v>901234591</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="1">
+        <v>39084</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64CBD805-FB40-4F13-A6A5-BD6B0B460E94}">
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="37.88671875" customWidth="1"/>
+    <col min="3" max="3" width="28.6640625" customWidth="1"/>
+    <col min="4" max="4" width="35.44140625" customWidth="1"/>
+    <col min="6" max="6" width="38.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2">
+        <v>901234592</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="1">
+        <v>39117</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3">
+        <v>901234593</v>
+      </c>
+      <c r="E3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" s="1">
+        <v>39147</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4">
+        <v>901234594</v>
+      </c>
+      <c r="E4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" s="1">
+        <v>39180</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D5">
+        <v>901234595</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="1">
+        <v>39212</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6">
+        <v>901234596</v>
+      </c>
+      <c r="E6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F6" s="1">
+        <v>39245</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7">
+        <v>901234597</v>
+      </c>
+      <c r="E7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F7" s="1">
+        <v>39277</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8">
+        <v>901234598</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="1">
+        <v>39310</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9">
+        <v>901234599</v>
+      </c>
+      <c r="E9" t="s">
+        <v>97</v>
+      </c>
+      <c r="F9" s="1">
+        <v>39343</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10">
+        <v>901234600</v>
+      </c>
+      <c r="E10" t="s">
+        <v>101</v>
+      </c>
+      <c r="F10" s="1">
+        <v>39375</v>
+      </c>
+      <c r="G10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11">
+        <v>901234601</v>
+      </c>
+      <c r="E11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="1">
+        <v>39408</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D12">
+        <v>123456789</v>
+      </c>
+      <c r="E12" t="s">
+        <v>126</v>
+      </c>
+      <c r="F12" s="1">
+        <v>39408</v>
+      </c>
+      <c r="G12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D13">
+        <v>123456789</v>
+      </c>
+      <c r="E13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="1">
+        <v>38021</v>
+      </c>
+      <c r="G13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>132</v>
+      </c>
+      <c r="B14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D14">
+        <v>123456789</v>
+      </c>
+      <c r="E14" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14" s="1">
+        <v>38021</v>
+      </c>
+      <c r="G14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" t="s">
+        <v>136</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D15">
+        <v>123456788</v>
+      </c>
+      <c r="E15" t="s">
+        <v>97</v>
+      </c>
+      <c r="F15" s="1">
+        <v>38021</v>
+      </c>
+      <c r="G15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16">
+        <v>123456777</v>
+      </c>
+      <c r="E16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" s="1">
+        <v>36892</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>143</v>
+      </c>
+      <c r="B17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D17">
+        <v>123456789</v>
+      </c>
+      <c r="E17" t="s">
+        <v>145</v>
+      </c>
+      <c r="F17" s="1">
+        <v>36892</v>
+      </c>
+      <c r="G17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C18" t="s">
+        <v>128</v>
+      </c>
+      <c r="D18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" t="s">
+        <v>147</v>
+      </c>
+      <c r="F18" t="s">
+        <v>128</v>
+      </c>
+      <c r="G18" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>148</v>
+      </c>
+      <c r="B19" t="s">
+        <v>149</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D19">
+        <v>123456789</v>
+      </c>
+      <c r="E19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="1">
+        <v>37987</v>
+      </c>
+      <c r="G19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>151</v>
+      </c>
+      <c r="B20" t="s">
+        <v>152</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D20">
+        <v>123456789</v>
+      </c>
+      <c r="E20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="1">
+        <v>36892</v>
+      </c>
+      <c r="G20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>154</v>
+      </c>
+      <c r="B21" t="s">
+        <v>155</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D21">
+        <v>123456789</v>
+      </c>
+      <c r="E21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="1">
+        <v>36892</v>
+      </c>
+      <c r="G21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>157</v>
+      </c>
+      <c r="B22" t="s">
+        <v>158</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D22">
+        <v>123456789</v>
+      </c>
+      <c r="E22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="1">
+        <v>36892</v>
+      </c>
+      <c r="G22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>160</v>
+      </c>
+      <c r="B23" t="s">
+        <v>161</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D23">
+        <v>123456790</v>
+      </c>
+      <c r="E23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="1">
+        <v>36893</v>
+      </c>
+      <c r="G23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B24" t="s">
+        <v>165</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D24">
+        <v>123456791</v>
+      </c>
+      <c r="E24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="1">
+        <v>36894</v>
+      </c>
+      <c r="G24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>164</v>
+      </c>
+      <c r="B25" t="s">
+        <v>167</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D25">
+        <v>123456792</v>
+      </c>
+      <c r="E25" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="1">
+        <v>36895</v>
+      </c>
+      <c r="G25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>169</v>
+      </c>
+      <c r="B26" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D26">
+        <v>123456793</v>
+      </c>
+      <c r="E26" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="1">
+        <v>36896</v>
+      </c>
+      <c r="G26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>172</v>
+      </c>
+      <c r="B27" t="s">
+        <v>174</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D27">
+        <v>123456794</v>
+      </c>
+      <c r="E27" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="1">
+        <v>36897</v>
+      </c>
+      <c r="G27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>173</v>
+      </c>
+      <c r="B28" t="s">
+        <v>176</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D28">
+        <v>123456795</v>
+      </c>
+      <c r="E28" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="1">
+        <v>47490</v>
+      </c>
+      <c r="G28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="20" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C12" r:id="rId1" xr:uid="{9EF190BC-0467-4877-BDA3-177A138B607B}"/>
+    <hyperlink ref="C13" r:id="rId2" xr:uid="{89DE7E01-0A64-4289-8807-B84637E752FD}"/>
+    <hyperlink ref="C14" r:id="rId3" xr:uid="{C0D218DE-2F58-40E6-83A1-FB1B0DDA9DA5}"/>
+    <hyperlink ref="C15" r:id="rId4" xr:uid="{564B7280-3EDC-402C-91DA-1307B66F6985}"/>
+    <hyperlink ref="C16" r:id="rId5" xr:uid="{9F56D980-05B6-4792-ADC3-6EFA175EB89D}"/>
+    <hyperlink ref="C17" r:id="rId6" xr:uid="{E4D3471D-F9CE-4DA0-868F-37730E5AB38B}"/>
+    <hyperlink ref="C19" r:id="rId7" xr:uid="{90634BFB-4A53-4CEE-A673-BC336AF85C1F}"/>
+    <hyperlink ref="C20" r:id="rId8" xr:uid="{FB8A14CE-0B74-48EB-A26F-2CAA0D3B713B}"/>
+    <hyperlink ref="C21" r:id="rId9" xr:uid="{DEBABF58-F010-4D52-A9C9-403A7AB9F353}"/>
+    <hyperlink ref="C22" r:id="rId10" xr:uid="{8FE31751-3312-497E-B731-893F6E49876D}"/>
+    <hyperlink ref="C23" r:id="rId11" xr:uid="{B81D7015-BAC5-4C49-AA4C-80FC86294A29}"/>
+    <hyperlink ref="C24" r:id="rId12" xr:uid="{EC71B839-4E18-4EFA-B457-0531E5B6DF30}"/>
+    <hyperlink ref="C25" r:id="rId13" xr:uid="{BCAF30E8-A778-4F43-9BB6-228A99FC951D}"/>
+    <hyperlink ref="C26" r:id="rId14" xr:uid="{16E75220-659F-4EA0-A2A7-FF324E21E93F}"/>
+    <hyperlink ref="C27" r:id="rId15" xr:uid="{8D15BD03-5795-487D-9D3C-224F5F77ACD6}"/>
+    <hyperlink ref="C28" r:id="rId16" xr:uid="{825467AF-FFAF-4782-A436-AFC37B9ECFFE}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/students_import2.xlsx
+++ b/students_import2.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\FPT\Sem9-SP26\SEP\EDUCEN-SEP490-\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEFAULT\FPT\SEP-G58\Code\EDUCEN-SEP490-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC619A51-2F18-4DAE-A1ED-D873049F4338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="students_import" sheetId="1" r:id="rId1"/>
@@ -23,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="181">
   <si>
     <t>Username</t>
   </si>
@@ -557,12 +556,21 @@
   </si>
   <si>
     <t>test057@gmail.com</t>
+  </si>
+  <si>
+    <t>nguyen van 58</t>
+  </si>
+  <si>
+    <t>test058@gmai.com</t>
+  </si>
+  <si>
+    <t>test058</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1388,19 +1396,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.88671875" customWidth="1"/>
-    <col min="2" max="2" width="31.109375" customWidth="1"/>
-    <col min="3" max="3" width="33.88671875" customWidth="1"/>
-    <col min="4" max="4" width="37.44140625" customWidth="1"/>
-    <col min="5" max="5" width="17.88671875" customWidth="1"/>
-    <col min="6" max="6" width="32.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" customWidth="1"/>
+    <col min="3" max="3" width="33.85546875" customWidth="1"/>
+    <col min="4" max="4" width="37.42578125" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" customWidth="1"/>
+    <col min="6" max="6" width="32.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1423,7 +1431,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1446,7 +1454,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1469,7 +1477,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1492,7 +1500,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1515,7 +1523,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1544,19 +1552,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88768A2A-C4B2-4A5B-B985-03C8CBA6A2F0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="33.33203125" customWidth="1"/>
-    <col min="3" max="3" width="35.33203125" customWidth="1"/>
-    <col min="4" max="4" width="25.44140625" customWidth="1"/>
-    <col min="5" max="5" width="21.5546875" customWidth="1"/>
-    <col min="6" max="6" width="36.21875" customWidth="1"/>
-    <col min="7" max="7" width="22.5546875" customWidth="1"/>
+    <col min="2" max="2" width="33.28515625" customWidth="1"/>
+    <col min="3" max="3" width="35.28515625" customWidth="1"/>
+    <col min="4" max="4" width="25.42578125" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" customWidth="1"/>
+    <col min="6" max="6" width="36.28515625" customWidth="1"/>
+    <col min="7" max="7" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1579,7 +1587,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1602,7 +1610,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -1625,7 +1633,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -1648,7 +1656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -1671,7 +1679,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -1694,7 +1702,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -1717,7 +1725,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -1740,7 +1748,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -1763,7 +1771,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -1786,7 +1794,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -1815,11 +1823,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06953985-C075-4BB3-A447-6CAD8C73ED67}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1842,7 +1850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -1865,7 +1873,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -1888,7 +1896,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -1911,7 +1919,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>70</v>
       </c>
@@ -1934,7 +1942,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>73</v>
       </c>
@@ -1957,7 +1965,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>76</v>
       </c>
@@ -1980,7 +1988,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>79</v>
       </c>
@@ -2003,7 +2011,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>82</v>
       </c>
@@ -2026,7 +2034,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>85</v>
       </c>
@@ -2049,7 +2057,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>88</v>
       </c>
@@ -2078,17 +2086,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64CBD805-FB40-4F13-A6A5-BD6B0B460E94}">
-  <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="37.88671875" customWidth="1"/>
-    <col min="3" max="3" width="28.6640625" customWidth="1"/>
-    <col min="4" max="4" width="35.44140625" customWidth="1"/>
-    <col min="6" max="6" width="38.77734375" customWidth="1"/>
+    <col min="2" max="2" width="37.85546875" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" customWidth="1"/>
+    <col min="4" max="4" width="35.42578125" customWidth="1"/>
+    <col min="6" max="6" width="38.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2111,7 +2119,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>91</v>
       </c>
@@ -2134,7 +2142,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>94</v>
       </c>
@@ -2157,7 +2165,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>98</v>
       </c>
@@ -2180,7 +2188,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>102</v>
       </c>
@@ -2203,7 +2211,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>105</v>
       </c>
@@ -2226,7 +2234,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>108</v>
       </c>
@@ -2249,7 +2257,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>111</v>
       </c>
@@ -2272,7 +2280,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>114</v>
       </c>
@@ -2295,7 +2303,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>117</v>
       </c>
@@ -2318,7 +2326,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>120</v>
       </c>
@@ -2341,7 +2349,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>123</v>
       </c>
@@ -2364,7 +2372,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>129</v>
       </c>
@@ -2387,7 +2395,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>132</v>
       </c>
@@ -2410,7 +2418,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>135</v>
       </c>
@@ -2433,7 +2441,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>138</v>
       </c>
@@ -2456,7 +2464,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>143</v>
       </c>
@@ -2479,7 +2487,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>127</v>
       </c>
@@ -2502,7 +2510,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>148</v>
       </c>
@@ -2525,7 +2533,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>151</v>
       </c>
@@ -2548,7 +2556,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>154</v>
       </c>
@@ -2571,7 +2579,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>157</v>
       </c>
@@ -2594,7 +2602,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>160</v>
       </c>
@@ -2617,7 +2625,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>163</v>
       </c>
@@ -2640,7 +2648,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>164</v>
       </c>
@@ -2663,7 +2671,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>169</v>
       </c>
@@ -2686,7 +2694,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>172</v>
       </c>
@@ -2709,7 +2717,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>173</v>
       </c>
@@ -2729,28 +2737,52 @@
         <v>47490</v>
       </c>
       <c r="G28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>180</v>
+      </c>
+      <c r="B29" t="s">
+        <v>178</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D29">
+        <v>123456789</v>
+      </c>
+      <c r="E29" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" s="1">
+        <v>44197</v>
+      </c>
+      <c r="G29" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="20" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C12" r:id="rId1" xr:uid="{9EF190BC-0467-4877-BDA3-177A138B607B}"/>
-    <hyperlink ref="C13" r:id="rId2" xr:uid="{89DE7E01-0A64-4289-8807-B84637E752FD}"/>
-    <hyperlink ref="C14" r:id="rId3" xr:uid="{C0D218DE-2F58-40E6-83A1-FB1B0DDA9DA5}"/>
-    <hyperlink ref="C15" r:id="rId4" xr:uid="{564B7280-3EDC-402C-91DA-1307B66F6985}"/>
-    <hyperlink ref="C16" r:id="rId5" xr:uid="{9F56D980-05B6-4792-ADC3-6EFA175EB89D}"/>
-    <hyperlink ref="C17" r:id="rId6" xr:uid="{E4D3471D-F9CE-4DA0-868F-37730E5AB38B}"/>
-    <hyperlink ref="C19" r:id="rId7" xr:uid="{90634BFB-4A53-4CEE-A673-BC336AF85C1F}"/>
-    <hyperlink ref="C20" r:id="rId8" xr:uid="{FB8A14CE-0B74-48EB-A26F-2CAA0D3B713B}"/>
-    <hyperlink ref="C21" r:id="rId9" xr:uid="{DEBABF58-F010-4D52-A9C9-403A7AB9F353}"/>
-    <hyperlink ref="C22" r:id="rId10" xr:uid="{8FE31751-3312-497E-B731-893F6E49876D}"/>
-    <hyperlink ref="C23" r:id="rId11" xr:uid="{B81D7015-BAC5-4C49-AA4C-80FC86294A29}"/>
-    <hyperlink ref="C24" r:id="rId12" xr:uid="{EC71B839-4E18-4EFA-B457-0531E5B6DF30}"/>
-    <hyperlink ref="C25" r:id="rId13" xr:uid="{BCAF30E8-A778-4F43-9BB6-228A99FC951D}"/>
-    <hyperlink ref="C26" r:id="rId14" xr:uid="{16E75220-659F-4EA0-A2A7-FF324E21E93F}"/>
-    <hyperlink ref="C27" r:id="rId15" xr:uid="{8D15BD03-5795-487D-9D3C-224F5F77ACD6}"/>
-    <hyperlink ref="C28" r:id="rId16" xr:uid="{825467AF-FFAF-4782-A436-AFC37B9ECFFE}"/>
+    <hyperlink ref="C12" r:id="rId1"/>
+    <hyperlink ref="C13" r:id="rId2"/>
+    <hyperlink ref="C14" r:id="rId3"/>
+    <hyperlink ref="C15" r:id="rId4"/>
+    <hyperlink ref="C16" r:id="rId5"/>
+    <hyperlink ref="C17" r:id="rId6"/>
+    <hyperlink ref="C19" r:id="rId7"/>
+    <hyperlink ref="C20" r:id="rId8"/>
+    <hyperlink ref="C21" r:id="rId9"/>
+    <hyperlink ref="C22" r:id="rId10"/>
+    <hyperlink ref="C23" r:id="rId11"/>
+    <hyperlink ref="C24" r:id="rId12"/>
+    <hyperlink ref="C25" r:id="rId13"/>
+    <hyperlink ref="C26" r:id="rId14"/>
+    <hyperlink ref="C27" r:id="rId15"/>
+    <hyperlink ref="C28" r:id="rId16"/>
+    <hyperlink ref="C29" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/students_import2.xlsx
+++ b/students_import2.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEFAULT\FPT\SEP-G58\Code\EDUCEN-SEP490-\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEP490\EDUCEN-SEP490-\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1B67A7-0D8B-4EC1-889A-DD1BA5B83A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="students_import" sheetId="1" r:id="rId1"/>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="42">
   <si>
     <t>Username</t>
   </si>
@@ -109,12 +110,51 @@
   </si>
   <si>
     <t>PhoneNumber</t>
+  </si>
+  <si>
+    <t>ParentName</t>
+  </si>
+  <si>
+    <t>ParentPhone</t>
+  </si>
+  <si>
+    <t>ParentEmail</t>
+  </si>
+  <si>
+    <t>Nguyen Van B1</t>
+  </si>
+  <si>
+    <t>Nguyen Van C1</t>
+  </si>
+  <si>
+    <t>Nguyen Van D1</t>
+  </si>
+  <si>
+    <t>Nguyen Van E1</t>
+  </si>
+  <si>
+    <t>test0101@email.com</t>
+  </si>
+  <si>
+    <t>test0102@email.com</t>
+  </si>
+  <si>
+    <t>test0103@email.com</t>
+  </si>
+  <si>
+    <t>test0104@email.com</t>
+  </si>
+  <si>
+    <t>test0105@email.com</t>
+  </si>
+  <si>
+    <t>Nguyen Van A1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -940,19 +980,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" customWidth="1"/>
-    <col min="2" max="2" width="31.140625" customWidth="1"/>
-    <col min="3" max="3" width="33.85546875" customWidth="1"/>
-    <col min="4" max="4" width="37.42578125" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" customWidth="1"/>
-    <col min="6" max="6" width="32.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.88671875" customWidth="1"/>
+    <col min="2" max="2" width="31.109375" customWidth="1"/>
+    <col min="3" max="3" width="33.88671875" customWidth="1"/>
+    <col min="4" max="4" width="37.44140625" customWidth="1"/>
+    <col min="5" max="5" width="17.88671875" customWidth="1"/>
+    <col min="6" max="6" width="32.6640625" customWidth="1"/>
+    <col min="8" max="8" width="16.21875" customWidth="1"/>
+    <col min="9" max="9" width="21.21875" customWidth="1"/>
+    <col min="10" max="10" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -974,8 +1017,17 @@
       <c r="G1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -997,8 +1049,17 @@
       <c r="G2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2">
+        <v>901234567</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1020,8 +1081,17 @@
       <c r="G3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3">
+        <v>901234568</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1043,8 +1113,17 @@
       <c r="G4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4">
+        <v>901234569</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1066,8 +1145,17 @@
       <c r="G5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5">
+        <v>901234570</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1089,54 +1177,70 @@
       <c r="G6" t="s">
         <v>10</v>
       </c>
+      <c r="H6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6">
+        <v>901234571</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>40</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J2" r:id="rId1" xr:uid="{2AC31191-FD24-448D-8094-A415C1C7FE95}"/>
+    <hyperlink ref="J3" r:id="rId2" xr:uid="{DD89A9E3-226F-4FE1-93F7-5EAF20A11EB6}"/>
+    <hyperlink ref="J4" r:id="rId3" xr:uid="{E3DCE1B6-55C2-4B9B-A22D-12F3E704A35F}"/>
+    <hyperlink ref="J5" r:id="rId4" xr:uid="{BC778F77-80DB-4AE1-A7C5-A6054CC69B78}"/>
+    <hyperlink ref="J6" r:id="rId5" xr:uid="{2A0A3230-BEFA-4262-9FC4-EA1C4AACE30B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="F2:F11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" customWidth="1"/>
-    <col min="2" max="2" width="33.28515625" customWidth="1"/>
-    <col min="3" max="3" width="35.28515625" customWidth="1"/>
-    <col min="4" max="4" width="35.5703125" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" customWidth="1"/>
-    <col min="6" max="6" width="36.28515625" customWidth="1"/>
-    <col min="7" max="7" width="22.5703125" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" customWidth="1"/>
+    <col min="2" max="2" width="33.33203125" customWidth="1"/>
+    <col min="3" max="3" width="35.33203125" customWidth="1"/>
+    <col min="4" max="4" width="35.5546875" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" customWidth="1"/>
+    <col min="6" max="6" width="36.33203125" customWidth="1"/>
+    <col min="7" max="7" width="22.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F9" s="1"/>
     </row>
-    <row r="10" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F11" s="1"/>
     </row>
   </sheetData>
@@ -1145,38 +1249,38 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="F2:F11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F9" s="1"/>
     </row>
-    <row r="10" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F11" s="1"/>
     </row>
   </sheetData>
@@ -1185,18 +1289,18 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="37.85546875" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" customWidth="1"/>
-    <col min="4" max="4" width="35.42578125" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" customWidth="1"/>
-    <col min="6" max="6" width="38.7109375" customWidth="1"/>
+    <col min="2" max="2" width="37.88671875" customWidth="1"/>
+    <col min="3" max="3" width="28.6640625" customWidth="1"/>
+    <col min="4" max="4" width="35.44140625" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" customWidth="1"/>
+    <col min="6" max="6" width="38.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1205,101 +1309,101 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F9" s="1"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C12" s="3"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C13" s="3"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C14" s="3"/>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C15" s="3"/>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C16" s="3"/>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C17" s="3"/>
       <c r="F17" s="1"/>
     </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C19" s="3"/>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C20" s="3"/>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C21" s="3"/>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C22" s="3"/>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C23" s="3"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C24" s="3"/>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C25" s="3"/>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C26" s="3"/>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C27" s="3"/>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C28" s="3"/>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C29" s="3"/>
       <c r="F29" s="1"/>
     </row>

--- a/students_import2.xlsx
+++ b/students_import2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEP490\EDUCEN-SEP490-\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\FPT\Sem9-SP26\SEP\EDUCEN-SEP490-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1B67A7-0D8B-4EC1-889A-DD1BA5B83A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463710D3-F5AA-47DD-B1A7-7D2F0A4ED1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="students_import" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
   <si>
     <t>Username</t>
   </si>
@@ -43,72 +43,12 @@
     <t>Gender</t>
   </si>
   <si>
-    <t>test001</t>
-  </si>
-  <si>
-    <t>Nguyen Van A</t>
-  </si>
-  <si>
-    <t>test001@email.com</t>
-  </si>
-  <si>
-    <t>10A</t>
-  </si>
-  <si>
     <t>Male</t>
   </si>
   <si>
-    <t>test002</t>
-  </si>
-  <si>
-    <t>Nguyen Van B</t>
-  </si>
-  <si>
-    <t>test002@email.com</t>
-  </si>
-  <si>
-    <t>10B</t>
-  </si>
-  <si>
     <t>Female</t>
   </si>
   <si>
-    <t>test003</t>
-  </si>
-  <si>
-    <t>Nguyen Van C</t>
-  </si>
-  <si>
-    <t>test003@email.com</t>
-  </si>
-  <si>
-    <t>11A</t>
-  </si>
-  <si>
-    <t>test004</t>
-  </si>
-  <si>
-    <t>Nguyen Van D</t>
-  </si>
-  <si>
-    <t>test004@email.com</t>
-  </si>
-  <si>
-    <t>11B</t>
-  </si>
-  <si>
-    <t>test005</t>
-  </si>
-  <si>
-    <t>Nguyen Van E</t>
-  </si>
-  <si>
-    <t>test005@email.com</t>
-  </si>
-  <si>
-    <t>12A</t>
-  </si>
-  <si>
     <t>PhoneNumber</t>
   </si>
   <si>
@@ -121,34 +61,58 @@
     <t>ParentEmail</t>
   </si>
   <si>
-    <t>Nguyen Van B1</t>
-  </si>
-  <si>
-    <t>Nguyen Van C1</t>
-  </si>
-  <si>
-    <t>Nguyen Van D1</t>
-  </si>
-  <si>
-    <t>Nguyen Van E1</t>
-  </si>
-  <si>
-    <t>test0101@email.com</t>
-  </si>
-  <si>
-    <t>test0102@email.com</t>
-  </si>
-  <si>
-    <t>test0103@email.com</t>
-  </si>
-  <si>
-    <t>test0104@email.com</t>
-  </si>
-  <si>
-    <t>test0105@email.com</t>
-  </si>
-  <si>
-    <t>Nguyen Van A1</t>
+    <t>Nguyễn Hồng Chi</t>
+  </si>
+  <si>
+    <t>Trần Ngọc Trang</t>
+  </si>
+  <si>
+    <t>tranngoctrang@gmail.com</t>
+  </si>
+  <si>
+    <t>nguyenhongchi@gmail.com</t>
+  </si>
+  <si>
+    <t>Ngô Mai Anh</t>
+  </si>
+  <si>
+    <t>ngomaianh@gmail.com</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Nguyên</t>
+  </si>
+  <si>
+    <t>nguyenhoangnguyen@gmail.com</t>
+  </si>
+  <si>
+    <t>blong8444@gmail.com</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Bảo Long</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Đức</t>
+  </si>
+  <si>
+    <t>anhquangmail.com</t>
+  </si>
+  <si>
+    <t>Nguyễn Anh Quân</t>
+  </si>
+  <si>
+    <t>anhquan@gmail.com</t>
+  </si>
+  <si>
+    <t>aaaaaaaaaaa</t>
+  </si>
+  <si>
+    <t>Nguyễn Anh Trung</t>
+  </si>
+  <si>
+    <t>phuhuynhquan@gmail.com</t>
+  </si>
+  <si>
+    <t>longncbhe171893@fpt.edu.vn</t>
   </si>
 </sst>
 </file>
@@ -981,10 +945,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.88671875" customWidth="1"/>
+    <col min="1" max="1" width="31.44140625" customWidth="1"/>
     <col min="2" max="2" width="31.109375" customWidth="1"/>
     <col min="3" max="3" width="33.88671875" customWidth="1"/>
     <col min="4" max="4" width="37.44140625" customWidth="1"/>
@@ -992,7 +956,7 @@
     <col min="6" max="6" width="32.6640625" customWidth="1"/>
     <col min="8" max="8" width="16.21875" customWidth="1"/>
     <col min="9" max="9" width="21.21875" customWidth="1"/>
-    <col min="10" max="10" width="12.88671875" customWidth="1"/>
+    <col min="10" max="10" width="25.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -1006,7 +970,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -1018,182 +982,199 @@
         <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="I1" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>6</v>
+      <c r="A2" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
+        <v>12</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D2">
-        <v>901234567</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
+        <v>914214477</v>
+      </c>
+      <c r="E2">
+        <v>10</v>
       </c>
       <c r="F2" s="1">
         <v>38353</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I2">
-        <v>901234567</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>11</v>
+      <c r="A3" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
         <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="D3">
         <v>901234568</v>
       </c>
-      <c r="E3" t="s">
-        <v>14</v>
+      <c r="E3">
+        <v>10</v>
       </c>
       <c r="F3" s="1">
         <v>38398</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I3">
         <v>901234568</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
       </c>
       <c r="D4">
         <v>901234569</v>
       </c>
-      <c r="E4" t="s">
-        <v>19</v>
+      <c r="E4">
+        <v>9</v>
       </c>
       <c r="F4" s="1">
         <v>38431</v>
       </c>
       <c r="G4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4">
-        <v>901234569</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>38</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>20</v>
+      <c r="A5" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D5">
         <v>901234570</v>
       </c>
-      <c r="E5" t="s">
-        <v>23</v>
+      <c r="E5">
+        <v>9</v>
       </c>
       <c r="F5" s="1">
         <v>38467</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5">
-        <v>901234570</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>39</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>24</v>
+      <c r="A6" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
+        <v>21</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="D6">
         <v>901234571</v>
       </c>
-      <c r="E6" t="s">
-        <v>27</v>
+      <c r="E6">
+        <v>8</v>
       </c>
       <c r="F6" s="1">
         <v>38482</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H6" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="I6">
         <v>901234571</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7">
+        <v>7</v>
+      </c>
+      <c r="F7" s="1">
+        <v>38483</v>
+      </c>
+      <c r="G7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7">
+        <v>972461842</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1" xr:uid="{2AC31191-FD24-448D-8094-A415C1C7FE95}"/>
-    <hyperlink ref="J3" r:id="rId2" xr:uid="{DD89A9E3-226F-4FE1-93F7-5EAF20A11EB6}"/>
-    <hyperlink ref="J4" r:id="rId3" xr:uid="{E3DCE1B6-55C2-4B9B-A22D-12F3E704A35F}"/>
-    <hyperlink ref="J5" r:id="rId4" xr:uid="{BC778F77-80DB-4AE1-A7C5-A6054CC69B78}"/>
-    <hyperlink ref="J6" r:id="rId5" xr:uid="{2A0A3230-BEFA-4262-9FC4-EA1C4AACE30B}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{EEF94E73-B438-411A-A69D-E96A370C6374}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{5A0A23CF-A351-404E-AD1A-8DC2D53F8C37}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{AA02EBC1-6FD4-4AEA-B261-9205E2433A78}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{F288F040-6BAB-457B-891F-298E2074A269}"/>
+    <hyperlink ref="A2" r:id="rId5" xr:uid="{55D10AD7-84E5-490B-A392-18882BF80321}"/>
+    <hyperlink ref="A3" r:id="rId6" xr:uid="{BC26971F-B603-4B6B-A26C-5F8B16600054}"/>
+    <hyperlink ref="A4" r:id="rId7" xr:uid="{D0008A62-0BBF-4868-ACE8-70F891D7C9DA}"/>
+    <hyperlink ref="A5" r:id="rId8" xr:uid="{368448C4-0880-4930-BACA-68DB4EC51C34}"/>
+    <hyperlink ref="A6" r:id="rId9" xr:uid="{CC62A3F3-1DE5-456E-A8EB-EADED25ABE3A}"/>
+    <hyperlink ref="C6" r:id="rId10" xr:uid="{928C1C2A-1B70-4F42-9FD7-40245A712B41}"/>
+    <hyperlink ref="A7" r:id="rId11" xr:uid="{3E8BCEAF-6093-4435-BB02-0DE82C227BFE}"/>
+    <hyperlink ref="J7" r:id="rId12" xr:uid="{2734FED3-7DCE-4DC8-9664-2F07296EA5D1}"/>
+    <hyperlink ref="J6" r:id="rId13" xr:uid="{70E6D6CF-9D32-4E2D-A558-511086877BBD}"/>
+    <hyperlink ref="J3" r:id="rId14" xr:uid="{BBBE1BB2-3169-477C-88CD-F1D7BFBCA410}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
